--- a/applications/Job_Matches_Paris_ProductAI.xlsx
+++ b/applications/Job_Matches_Paris_ProductAI.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1260"/>
+  <dimension ref="A1:M1347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -45056,8 +45056,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F951" t="inlineStr"/>
-      <c r="G951" t="inlineStr"/>
       <c r="H951" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45101,8 +45099,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F952" t="inlineStr"/>
-      <c r="G952" t="inlineStr"/>
       <c r="H952" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45146,8 +45142,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F953" t="inlineStr"/>
-      <c r="G953" t="inlineStr"/>
       <c r="H953" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45191,8 +45185,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F954" t="inlineStr"/>
-      <c r="G954" t="inlineStr"/>
       <c r="H954" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45236,7 +45228,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F955" t="inlineStr"/>
       <c r="G955" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -45285,8 +45276,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F956" t="inlineStr"/>
-      <c r="G956" t="inlineStr"/>
       <c r="H956" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45330,8 +45319,6 @@
           <t>Montigny-le-Bretonneux</t>
         </is>
       </c>
-      <c r="F957" t="inlineStr"/>
-      <c r="G957" t="inlineStr"/>
       <c r="H957" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45375,8 +45362,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F958" t="inlineStr"/>
-      <c r="G958" t="inlineStr"/>
       <c r="H958" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45420,8 +45405,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F959" t="inlineStr"/>
-      <c r="G959" t="inlineStr"/>
       <c r="H959" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45465,8 +45448,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F960" t="inlineStr"/>
-      <c r="G960" t="inlineStr"/>
       <c r="H960" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45510,8 +45491,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F961" t="inlineStr"/>
-      <c r="G961" t="inlineStr"/>
       <c r="H961" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45555,8 +45534,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F962" t="inlineStr"/>
-      <c r="G962" t="inlineStr"/>
       <c r="H962" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45600,8 +45577,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F963" t="inlineStr"/>
-      <c r="G963" t="inlineStr"/>
       <c r="H963" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45645,8 +45620,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F964" t="inlineStr"/>
-      <c r="G964" t="inlineStr"/>
       <c r="H964" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45690,8 +45663,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F965" t="inlineStr"/>
-      <c r="G965" t="inlineStr"/>
       <c r="H965" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45735,8 +45706,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F966" t="inlineStr"/>
-      <c r="G966" t="inlineStr"/>
       <c r="H966" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45780,8 +45749,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F967" t="inlineStr"/>
-      <c r="G967" t="inlineStr"/>
       <c r="H967" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45825,8 +45792,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F968" t="inlineStr"/>
-      <c r="G968" t="inlineStr"/>
       <c r="H968" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45870,8 +45835,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F969" t="inlineStr"/>
-      <c r="G969" t="inlineStr"/>
       <c r="H969" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45915,8 +45878,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F970" t="inlineStr"/>
-      <c r="G970" t="inlineStr"/>
       <c r="H970" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -45960,8 +45921,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F971" t="inlineStr"/>
-      <c r="G971" t="inlineStr"/>
       <c r="H971" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46005,8 +45964,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F972" t="inlineStr"/>
-      <c r="G972" t="inlineStr"/>
       <c r="H972" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46050,8 +46007,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F973" t="inlineStr"/>
-      <c r="G973" t="inlineStr"/>
       <c r="H973" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46095,8 +46050,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F974" t="inlineStr"/>
-      <c r="G974" t="inlineStr"/>
       <c r="H974" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46140,8 +46093,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F975" t="inlineStr"/>
-      <c r="G975" t="inlineStr"/>
       <c r="H975" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46185,8 +46136,6 @@
           <t>Courbevoie</t>
         </is>
       </c>
-      <c r="F976" t="inlineStr"/>
-      <c r="G976" t="inlineStr"/>
       <c r="H976" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46230,8 +46179,6 @@
           <t>Courbevoie</t>
         </is>
       </c>
-      <c r="F977" t="inlineStr"/>
-      <c r="G977" t="inlineStr"/>
       <c r="H977" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46275,8 +46222,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F978" t="inlineStr"/>
-      <c r="G978" t="inlineStr"/>
       <c r="H978" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46320,8 +46265,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F979" t="inlineStr"/>
-      <c r="G979" t="inlineStr"/>
       <c r="H979" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46365,8 +46308,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F980" t="inlineStr"/>
-      <c r="G980" t="inlineStr"/>
       <c r="H980" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46410,8 +46351,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F981" t="inlineStr"/>
-      <c r="G981" t="inlineStr"/>
       <c r="H981" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46455,8 +46394,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F982" t="inlineStr"/>
-      <c r="G982" t="inlineStr"/>
       <c r="H982" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46500,8 +46437,6 @@
           <t>Issy-les-Moulineaux</t>
         </is>
       </c>
-      <c r="F983" t="inlineStr"/>
-      <c r="G983" t="inlineStr"/>
       <c r="H983" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46545,8 +46480,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F984" t="inlineStr"/>
-      <c r="G984" t="inlineStr"/>
       <c r="H984" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46590,7 +46523,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F985" t="inlineStr"/>
       <c r="G985" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -46639,7 +46571,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F986" t="inlineStr"/>
       <c r="G986" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -46688,8 +46619,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F987" t="inlineStr"/>
-      <c r="G987" t="inlineStr"/>
       <c r="H987" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46733,8 +46662,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F988" t="inlineStr"/>
-      <c r="G988" t="inlineStr"/>
       <c r="H988" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46778,8 +46705,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F989" t="inlineStr"/>
-      <c r="G989" t="inlineStr"/>
       <c r="H989" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46823,8 +46748,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F990" t="inlineStr"/>
-      <c r="G990" t="inlineStr"/>
       <c r="H990" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46868,8 +46791,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F991" t="inlineStr"/>
-      <c r="G991" t="inlineStr"/>
       <c r="H991" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46913,8 +46834,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F992" t="inlineStr"/>
-      <c r="G992" t="inlineStr"/>
       <c r="H992" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -46958,8 +46877,6 @@
           <t>Courbevoie</t>
         </is>
       </c>
-      <c r="F993" t="inlineStr"/>
-      <c r="G993" t="inlineStr"/>
       <c r="H993" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47003,8 +46920,6 @@
           <t>Montreuil</t>
         </is>
       </c>
-      <c r="F994" t="inlineStr"/>
-      <c r="G994" t="inlineStr"/>
       <c r="H994" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47048,8 +46963,6 @@
           <t>Clichy</t>
         </is>
       </c>
-      <c r="F995" t="inlineStr"/>
-      <c r="G995" t="inlineStr"/>
       <c r="H995" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47093,8 +47006,6 @@
           <t>Montrouge</t>
         </is>
       </c>
-      <c r="F996" t="inlineStr"/>
-      <c r="G996" t="inlineStr"/>
       <c r="H996" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47138,8 +47049,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F997" t="inlineStr"/>
-      <c r="G997" t="inlineStr"/>
       <c r="H997" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47183,8 +47092,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F998" t="inlineStr"/>
-      <c r="G998" t="inlineStr"/>
       <c r="H998" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47228,8 +47135,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F999" t="inlineStr"/>
-      <c r="G999" t="inlineStr"/>
       <c r="H999" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47273,8 +47178,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1000" t="inlineStr"/>
-      <c r="G1000" t="inlineStr"/>
       <c r="H1000" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47318,7 +47221,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1001" t="inlineStr"/>
       <c r="G1001" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -47367,8 +47269,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1002" t="inlineStr"/>
-      <c r="G1002" t="inlineStr"/>
       <c r="H1002" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47412,8 +47312,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1003" t="inlineStr"/>
-      <c r="G1003" t="inlineStr"/>
       <c r="H1003" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47457,8 +47355,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1004" t="inlineStr"/>
-      <c r="G1004" t="inlineStr"/>
       <c r="H1004" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47502,7 +47398,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1005" t="inlineStr"/>
       <c r="G1005" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -47551,8 +47446,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1006" t="inlineStr"/>
-      <c r="G1006" t="inlineStr"/>
       <c r="H1006" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47596,8 +47489,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1007" t="inlineStr"/>
-      <c r="G1007" t="inlineStr"/>
       <c r="H1007" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47641,8 +47532,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F1008" t="inlineStr"/>
-      <c r="G1008" t="inlineStr"/>
       <c r="H1008" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47686,8 +47575,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1009" t="inlineStr"/>
-      <c r="G1009" t="inlineStr"/>
       <c r="H1009" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47731,8 +47618,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1010" t="inlineStr"/>
-      <c r="G1010" t="inlineStr"/>
       <c r="H1010" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47776,8 +47661,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1011" t="inlineStr"/>
-      <c r="G1011" t="inlineStr"/>
       <c r="H1011" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47821,8 +47704,6 @@
           <t>Courbevoie</t>
         </is>
       </c>
-      <c r="F1012" t="inlineStr"/>
-      <c r="G1012" t="inlineStr"/>
       <c r="H1012" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47866,8 +47747,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1013" t="inlineStr"/>
-      <c r="G1013" t="inlineStr"/>
       <c r="H1013" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47911,8 +47790,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1014" t="inlineStr"/>
-      <c r="G1014" t="inlineStr"/>
       <c r="H1014" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -47956,8 +47833,6 @@
           <t>France</t>
         </is>
       </c>
-      <c r="F1015" t="inlineStr"/>
-      <c r="G1015" t="inlineStr"/>
       <c r="H1015" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48001,8 +47876,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1016" t="inlineStr"/>
-      <c r="G1016" t="inlineStr"/>
       <c r="H1016" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48046,8 +47919,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1017" t="inlineStr"/>
-      <c r="G1017" t="inlineStr"/>
       <c r="H1017" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48091,8 +47962,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1018" t="inlineStr"/>
-      <c r="G1018" t="inlineStr"/>
       <c r="H1018" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48136,8 +48005,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1019" t="inlineStr"/>
-      <c r="G1019" t="inlineStr"/>
       <c r="H1019" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48181,8 +48048,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1020" t="inlineStr"/>
-      <c r="G1020" t="inlineStr"/>
       <c r="H1020" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48226,8 +48091,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1021" t="inlineStr"/>
-      <c r="G1021" t="inlineStr"/>
       <c r="H1021" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48271,8 +48134,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1022" t="inlineStr"/>
-      <c r="G1022" t="inlineStr"/>
       <c r="H1022" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48316,8 +48177,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F1023" t="inlineStr"/>
-      <c r="G1023" t="inlineStr"/>
       <c r="H1023" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48361,8 +48220,6 @@
           <t>Boulogne-Billancourt</t>
         </is>
       </c>
-      <c r="F1024" t="inlineStr"/>
-      <c r="G1024" t="inlineStr"/>
       <c r="H1024" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48406,8 +48263,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1025" t="inlineStr"/>
-      <c r="G1025" t="inlineStr"/>
       <c r="H1025" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48451,8 +48306,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1026" t="inlineStr"/>
-      <c r="G1026" t="inlineStr"/>
       <c r="H1026" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48496,8 +48349,6 @@
           <t>Montrouge</t>
         </is>
       </c>
-      <c r="F1027" t="inlineStr"/>
-      <c r="G1027" t="inlineStr"/>
       <c r="H1027" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48541,8 +48392,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1028" t="inlineStr"/>
-      <c r="G1028" t="inlineStr"/>
       <c r="H1028" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48586,8 +48435,6 @@
           <t>Puteaux</t>
         </is>
       </c>
-      <c r="F1029" t="inlineStr"/>
-      <c r="G1029" t="inlineStr"/>
       <c r="H1029" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48631,8 +48478,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1030" t="inlineStr"/>
-      <c r="G1030" t="inlineStr"/>
       <c r="H1030" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48676,8 +48521,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1031" t="inlineStr"/>
-      <c r="G1031" t="inlineStr"/>
       <c r="H1031" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48721,8 +48564,6 @@
           <t>Issy-les-Moulineaux</t>
         </is>
       </c>
-      <c r="F1032" t="inlineStr"/>
-      <c r="G1032" t="inlineStr"/>
       <c r="H1032" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48766,8 +48607,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1033" t="inlineStr"/>
-      <c r="G1033" t="inlineStr"/>
       <c r="H1033" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48811,8 +48650,6 @@
           <t>Issy-les-Moulineaux</t>
         </is>
       </c>
-      <c r="F1034" t="inlineStr"/>
-      <c r="G1034" t="inlineStr"/>
       <c r="H1034" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48856,8 +48693,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1035" t="inlineStr"/>
-      <c r="G1035" t="inlineStr"/>
       <c r="H1035" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48901,8 +48736,6 @@
           <t>Villepinte</t>
         </is>
       </c>
-      <c r="F1036" t="inlineStr"/>
-      <c r="G1036" t="inlineStr"/>
       <c r="H1036" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48946,8 +48779,6 @@
           <t>Saint-Denis</t>
         </is>
       </c>
-      <c r="F1037" t="inlineStr"/>
-      <c r="G1037" t="inlineStr"/>
       <c r="H1037" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -48991,8 +48822,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1038" t="inlineStr"/>
-      <c r="G1038" t="inlineStr"/>
       <c r="H1038" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49036,8 +48865,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1039" t="inlineStr"/>
-      <c r="G1039" t="inlineStr"/>
       <c r="H1039" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49081,8 +48908,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1040" t="inlineStr"/>
-      <c r="G1040" t="inlineStr"/>
       <c r="H1040" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49126,8 +48951,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1041" t="inlineStr"/>
-      <c r="G1041" t="inlineStr"/>
       <c r="H1041" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49171,8 +48994,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1042" t="inlineStr"/>
-      <c r="G1042" t="inlineStr"/>
       <c r="H1042" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49216,8 +49037,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1043" t="inlineStr"/>
-      <c r="G1043" t="inlineStr"/>
       <c r="H1043" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49261,8 +49080,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F1044" t="inlineStr"/>
-      <c r="G1044" t="inlineStr"/>
       <c r="H1044" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49306,8 +49123,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1045" t="inlineStr"/>
-      <c r="G1045" t="inlineStr"/>
       <c r="H1045" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49351,8 +49166,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1046" t="inlineStr"/>
-      <c r="G1046" t="inlineStr"/>
       <c r="H1046" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49396,8 +49209,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1047" t="inlineStr"/>
-      <c r="G1047" t="inlineStr"/>
       <c r="H1047" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49441,8 +49252,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1048" t="inlineStr"/>
-      <c r="G1048" t="inlineStr"/>
       <c r="H1048" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49486,8 +49295,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1049" t="inlineStr"/>
-      <c r="G1049" t="inlineStr"/>
       <c r="H1049" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49531,8 +49338,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1050" t="inlineStr"/>
-      <c r="G1050" t="inlineStr"/>
       <c r="H1050" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49576,8 +49381,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1051" t="inlineStr"/>
-      <c r="G1051" t="inlineStr"/>
       <c r="H1051" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49621,8 +49424,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F1052" t="inlineStr"/>
-      <c r="G1052" t="inlineStr"/>
       <c r="H1052" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49666,8 +49467,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1053" t="inlineStr"/>
-      <c r="G1053" t="inlineStr"/>
       <c r="H1053" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49711,8 +49510,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1054" t="inlineStr"/>
-      <c r="G1054" t="inlineStr"/>
       <c r="H1054" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49756,8 +49553,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1055" t="inlineStr"/>
-      <c r="G1055" t="inlineStr"/>
       <c r="H1055" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49801,8 +49596,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1056" t="inlineStr"/>
-      <c r="G1056" t="inlineStr"/>
       <c r="H1056" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49846,8 +49639,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1057" t="inlineStr"/>
-      <c r="G1057" t="inlineStr"/>
       <c r="H1057" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49891,8 +49682,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1058" t="inlineStr"/>
-      <c r="G1058" t="inlineStr"/>
       <c r="H1058" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49936,8 +49725,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1059" t="inlineStr"/>
-      <c r="G1059" t="inlineStr"/>
       <c r="H1059" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -49981,8 +49768,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F1060" t="inlineStr"/>
-      <c r="G1060" t="inlineStr"/>
       <c r="H1060" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50026,8 +49811,6 @@
           <t>Nanterre</t>
         </is>
       </c>
-      <c r="F1061" t="inlineStr"/>
-      <c r="G1061" t="inlineStr"/>
       <c r="H1061" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50071,8 +49854,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1062" t="inlineStr"/>
-      <c r="G1062" t="inlineStr"/>
       <c r="H1062" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50116,8 +49897,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1063" t="inlineStr"/>
-      <c r="G1063" t="inlineStr"/>
       <c r="H1063" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50161,7 +49940,6 @@
           <t>Chalon-sur-Saône</t>
         </is>
       </c>
-      <c r="F1064" t="inlineStr"/>
       <c r="G1064" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -50210,7 +49988,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1065" t="inlineStr"/>
       <c r="G1065" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -50259,7 +50036,6 @@
           <t>Bordeaux</t>
         </is>
       </c>
-      <c r="F1066" t="inlineStr"/>
       <c r="G1066" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -50308,8 +50084,6 @@
           <t>Boulogne-Billancourt</t>
         </is>
       </c>
-      <c r="F1067" t="inlineStr"/>
-      <c r="G1067" t="inlineStr"/>
       <c r="H1067" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50353,7 +50127,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1068" t="inlineStr"/>
       <c r="G1068" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -50402,8 +50175,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1069" t="inlineStr"/>
-      <c r="G1069" t="inlineStr"/>
       <c r="H1069" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50447,8 +50218,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1070" t="inlineStr"/>
-      <c r="G1070" t="inlineStr"/>
       <c r="H1070" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50492,8 +50261,6 @@
           <t>Nanterre</t>
         </is>
       </c>
-      <c r="F1071" t="inlineStr"/>
-      <c r="G1071" t="inlineStr"/>
       <c r="H1071" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50537,8 +50304,6 @@
           <t>Nanterre</t>
         </is>
       </c>
-      <c r="F1072" t="inlineStr"/>
-      <c r="G1072" t="inlineStr"/>
       <c r="H1072" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50582,8 +50347,6 @@
           <t>Nanterre</t>
         </is>
       </c>
-      <c r="F1073" t="inlineStr"/>
-      <c r="G1073" t="inlineStr"/>
       <c r="H1073" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50627,8 +50390,6 @@
           <t>Boulogne-Billancourt</t>
         </is>
       </c>
-      <c r="F1074" t="inlineStr"/>
-      <c r="G1074" t="inlineStr"/>
       <c r="H1074" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50672,8 +50433,6 @@
           <t>Boulogne-Billancourt</t>
         </is>
       </c>
-      <c r="F1075" t="inlineStr"/>
-      <c r="G1075" t="inlineStr"/>
       <c r="H1075" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50717,7 +50476,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1076" t="inlineStr"/>
       <c r="G1076" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -50766,7 +50524,6 @@
           <t>Maisons-Alfort</t>
         </is>
       </c>
-      <c r="F1077" t="inlineStr"/>
       <c r="G1077" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -50815,7 +50572,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1078" t="inlineStr"/>
       <c r="G1078" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -50864,8 +50620,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1079" t="inlineStr"/>
-      <c r="G1079" t="inlineStr"/>
       <c r="H1079" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50909,8 +50663,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1080" t="inlineStr"/>
-      <c r="G1080" t="inlineStr"/>
       <c r="H1080" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50954,8 +50706,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F1081" t="inlineStr"/>
-      <c r="G1081" t="inlineStr"/>
       <c r="H1081" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -50999,8 +50749,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1082" t="inlineStr"/>
-      <c r="G1082" t="inlineStr"/>
       <c r="H1082" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51044,8 +50792,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1083" t="inlineStr"/>
-      <c r="G1083" t="inlineStr"/>
       <c r="H1083" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51089,8 +50835,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1084" t="inlineStr"/>
-      <c r="G1084" t="inlineStr"/>
       <c r="H1084" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51134,8 +50878,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1085" t="inlineStr"/>
-      <c r="G1085" t="inlineStr"/>
       <c r="H1085" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51179,8 +50921,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1086" t="inlineStr"/>
-      <c r="G1086" t="inlineStr"/>
       <c r="H1086" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51224,8 +50964,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1087" t="inlineStr"/>
-      <c r="G1087" t="inlineStr"/>
       <c r="H1087" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51269,8 +51007,6 @@
           <t>Buc</t>
         </is>
       </c>
-      <c r="F1088" t="inlineStr"/>
-      <c r="G1088" t="inlineStr"/>
       <c r="H1088" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51314,8 +51050,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1089" t="inlineStr"/>
-      <c r="G1089" t="inlineStr"/>
       <c r="H1089" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51359,8 +51093,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F1090" t="inlineStr"/>
-      <c r="G1090" t="inlineStr"/>
       <c r="H1090" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51404,7 +51136,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1091" t="inlineStr"/>
       <c r="G1091" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -51453,8 +51184,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1092" t="inlineStr"/>
-      <c r="G1092" t="inlineStr"/>
       <c r="H1092" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51498,8 +51227,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1093" t="inlineStr"/>
-      <c r="G1093" t="inlineStr"/>
       <c r="H1093" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51543,8 +51270,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1094" t="inlineStr"/>
-      <c r="G1094" t="inlineStr"/>
       <c r="H1094" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51588,8 +51313,6 @@
           <t>Guyancourt</t>
         </is>
       </c>
-      <c r="F1095" t="inlineStr"/>
-      <c r="G1095" t="inlineStr"/>
       <c r="H1095" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51633,8 +51356,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1096" t="inlineStr"/>
-      <c r="G1096" t="inlineStr"/>
       <c r="H1096" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51678,8 +51399,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1097" t="inlineStr"/>
-      <c r="G1097" t="inlineStr"/>
       <c r="H1097" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51723,7 +51442,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1098" t="inlineStr"/>
       <c r="G1098" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -51772,8 +51490,6 @@
           <t>Issy-les-Moulineaux</t>
         </is>
       </c>
-      <c r="F1099" t="inlineStr"/>
-      <c r="G1099" t="inlineStr"/>
       <c r="H1099" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51817,8 +51533,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1100" t="inlineStr"/>
-      <c r="G1100" t="inlineStr"/>
       <c r="H1100" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51862,8 +51576,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1101" t="inlineStr"/>
-      <c r="G1101" t="inlineStr"/>
       <c r="H1101" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51907,8 +51619,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1102" t="inlineStr"/>
-      <c r="G1102" t="inlineStr"/>
       <c r="H1102" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51952,8 +51662,6 @@
           <t>Rueil-Malmaison</t>
         </is>
       </c>
-      <c r="F1103" t="inlineStr"/>
-      <c r="G1103" t="inlineStr"/>
       <c r="H1103" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -51997,8 +51705,6 @@
           <t>Bois-Colombes</t>
         </is>
       </c>
-      <c r="F1104" t="inlineStr"/>
-      <c r="G1104" t="inlineStr"/>
       <c r="H1104" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52042,8 +51748,6 @@
           <t>Bois-Colombes</t>
         </is>
       </c>
-      <c r="F1105" t="inlineStr"/>
-      <c r="G1105" t="inlineStr"/>
       <c r="H1105" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52087,8 +51791,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1106" t="inlineStr"/>
-      <c r="G1106" t="inlineStr"/>
       <c r="H1106" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52132,8 +51834,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1107" t="inlineStr"/>
-      <c r="G1107" t="inlineStr"/>
       <c r="H1107" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52177,8 +51877,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1108" t="inlineStr"/>
-      <c r="G1108" t="inlineStr"/>
       <c r="H1108" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52222,8 +51920,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1109" t="inlineStr"/>
-      <c r="G1109" t="inlineStr"/>
       <c r="H1109" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52267,8 +51963,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1110" t="inlineStr"/>
-      <c r="G1110" t="inlineStr"/>
       <c r="H1110" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52312,8 +52006,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1111" t="inlineStr"/>
-      <c r="G1111" t="inlineStr"/>
       <c r="H1111" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52357,8 +52049,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1112" t="inlineStr"/>
-      <c r="G1112" t="inlineStr"/>
       <c r="H1112" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52402,8 +52092,6 @@
           <t>Boulogne-Billancourt</t>
         </is>
       </c>
-      <c r="F1113" t="inlineStr"/>
-      <c r="G1113" t="inlineStr"/>
       <c r="H1113" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52447,8 +52135,6 @@
           <t>Boulogne-Billancourt</t>
         </is>
       </c>
-      <c r="F1114" t="inlineStr"/>
-      <c r="G1114" t="inlineStr"/>
       <c r="H1114" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52492,8 +52178,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1115" t="inlineStr"/>
-      <c r="G1115" t="inlineStr"/>
       <c r="H1115" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52537,8 +52221,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1116" t="inlineStr"/>
-      <c r="G1116" t="inlineStr"/>
       <c r="H1116" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52582,8 +52264,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1117" t="inlineStr"/>
-      <c r="G1117" t="inlineStr"/>
       <c r="H1117" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52627,8 +52307,6 @@
           <t>Puteaux</t>
         </is>
       </c>
-      <c r="F1118" t="inlineStr"/>
-      <c r="G1118" t="inlineStr"/>
       <c r="H1118" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52672,8 +52350,6 @@
           <t>Puteaux</t>
         </is>
       </c>
-      <c r="F1119" t="inlineStr"/>
-      <c r="G1119" t="inlineStr"/>
       <c r="H1119" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52717,7 +52393,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1120" t="inlineStr"/>
       <c r="G1120" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -52766,8 +52441,6 @@
           <t>Maisons-Alfort</t>
         </is>
       </c>
-      <c r="F1121" t="inlineStr"/>
-      <c r="G1121" t="inlineStr"/>
       <c r="H1121" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52811,8 +52484,6 @@
           <t>Massy</t>
         </is>
       </c>
-      <c r="F1122" t="inlineStr"/>
-      <c r="G1122" t="inlineStr"/>
       <c r="H1122" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52856,8 +52527,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1123" t="inlineStr"/>
-      <c r="G1123" t="inlineStr"/>
       <c r="H1123" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52901,8 +52570,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1124" t="inlineStr"/>
-      <c r="G1124" t="inlineStr"/>
       <c r="H1124" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52946,8 +52613,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1125" t="inlineStr"/>
-      <c r="G1125" t="inlineStr"/>
       <c r="H1125" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -52991,8 +52656,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1126" t="inlineStr"/>
-      <c r="G1126" t="inlineStr"/>
       <c r="H1126" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53036,8 +52699,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1127" t="inlineStr"/>
-      <c r="G1127" t="inlineStr"/>
       <c r="H1127" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53081,8 +52742,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1128" t="inlineStr"/>
-      <c r="G1128" t="inlineStr"/>
       <c r="H1128" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53126,8 +52785,6 @@
           <t>Saint-Mandé</t>
         </is>
       </c>
-      <c r="F1129" t="inlineStr"/>
-      <c r="G1129" t="inlineStr"/>
       <c r="H1129" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53171,8 +52828,6 @@
           <t>Massy</t>
         </is>
       </c>
-      <c r="F1130" t="inlineStr"/>
-      <c r="G1130" t="inlineStr"/>
       <c r="H1130" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53216,8 +52871,6 @@
           <t>France</t>
         </is>
       </c>
-      <c r="F1131" t="inlineStr"/>
-      <c r="G1131" t="inlineStr"/>
       <c r="H1131" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53261,8 +52914,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1132" t="inlineStr"/>
-      <c r="G1132" t="inlineStr"/>
       <c r="H1132" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53306,8 +52957,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1133" t="inlineStr"/>
-      <c r="G1133" t="inlineStr"/>
       <c r="H1133" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53351,8 +53000,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1134" t="inlineStr"/>
-      <c r="G1134" t="inlineStr"/>
       <c r="H1134" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53396,8 +53043,6 @@
           <t>Saint-Denis</t>
         </is>
       </c>
-      <c r="F1135" t="inlineStr"/>
-      <c r="G1135" t="inlineStr"/>
       <c r="H1135" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53441,8 +53086,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1136" t="inlineStr"/>
-      <c r="G1136" t="inlineStr"/>
       <c r="H1136" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53486,8 +53129,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1137" t="inlineStr"/>
-      <c r="G1137" t="inlineStr"/>
       <c r="H1137" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53531,8 +53172,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1138" t="inlineStr"/>
-      <c r="G1138" t="inlineStr"/>
       <c r="H1138" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53576,8 +53215,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1139" t="inlineStr"/>
-      <c r="G1139" t="inlineStr"/>
       <c r="H1139" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53621,8 +53258,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1140" t="inlineStr"/>
-      <c r="G1140" t="inlineStr"/>
       <c r="H1140" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53666,8 +53301,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1141" t="inlineStr"/>
-      <c r="G1141" t="inlineStr"/>
       <c r="H1141" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53711,8 +53344,6 @@
           <t>Puteaux</t>
         </is>
       </c>
-      <c r="F1142" t="inlineStr"/>
-      <c r="G1142" t="inlineStr"/>
       <c r="H1142" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53756,8 +53387,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1143" t="inlineStr"/>
-      <c r="G1143" t="inlineStr"/>
       <c r="H1143" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53801,8 +53430,6 @@
           <t>Maisons-Alfort</t>
         </is>
       </c>
-      <c r="F1144" t="inlineStr"/>
-      <c r="G1144" t="inlineStr"/>
       <c r="H1144" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53846,8 +53473,6 @@
           <t>Maisons-Alfort</t>
         </is>
       </c>
-      <c r="F1145" t="inlineStr"/>
-      <c r="G1145" t="inlineStr"/>
       <c r="H1145" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53891,8 +53516,6 @@
           <t>Saint-Ouen</t>
         </is>
       </c>
-      <c r="F1146" t="inlineStr"/>
-      <c r="G1146" t="inlineStr"/>
       <c r="H1146" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53936,8 +53559,6 @@
           <t>Courbevoie</t>
         </is>
       </c>
-      <c r="F1147" t="inlineStr"/>
-      <c r="G1147" t="inlineStr"/>
       <c r="H1147" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -53981,8 +53602,6 @@
           <t>Issy-les-Moulineaux</t>
         </is>
       </c>
-      <c r="F1148" t="inlineStr"/>
-      <c r="G1148" t="inlineStr"/>
       <c r="H1148" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54026,7 +53645,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1149" t="inlineStr"/>
       <c r="G1149" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -54075,7 +53693,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1150" t="inlineStr"/>
       <c r="G1150" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -54124,7 +53741,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1151" t="inlineStr"/>
       <c r="G1151" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -54173,7 +53789,6 @@
           <t>Rueil-Malmaison</t>
         </is>
       </c>
-      <c r="F1152" t="inlineStr"/>
       <c r="G1152" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -54222,7 +53837,6 @@
           <t>Grenoble</t>
         </is>
       </c>
-      <c r="F1153" t="inlineStr"/>
       <c r="G1153" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -54271,8 +53885,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1154" t="inlineStr"/>
-      <c r="G1154" t="inlineStr"/>
       <c r="H1154" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54316,7 +53928,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1155" t="inlineStr"/>
       <c r="G1155" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -54365,7 +53976,6 @@
           <t>Marcoussis</t>
         </is>
       </c>
-      <c r="F1156" t="inlineStr"/>
       <c r="G1156" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -54414,8 +54024,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1157" t="inlineStr"/>
-      <c r="G1157" t="inlineStr"/>
       <c r="H1157" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54459,8 +54067,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1158" t="inlineStr"/>
-      <c r="G1158" t="inlineStr"/>
       <c r="H1158" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54504,8 +54110,6 @@
           <t>Gif-sur-Yvette</t>
         </is>
       </c>
-      <c r="F1159" t="inlineStr"/>
-      <c r="G1159" t="inlineStr"/>
       <c r="H1159" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54549,8 +54153,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1160" t="inlineStr"/>
-      <c r="G1160" t="inlineStr"/>
       <c r="H1160" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54594,8 +54196,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1161" t="inlineStr"/>
-      <c r="G1161" t="inlineStr"/>
       <c r="H1161" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54639,8 +54239,6 @@
           <t>Clichy</t>
         </is>
       </c>
-      <c r="F1162" t="inlineStr"/>
-      <c r="G1162" t="inlineStr"/>
       <c r="H1162" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54684,7 +54282,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1163" t="inlineStr"/>
       <c r="G1163" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -54733,7 +54330,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1164" t="inlineStr"/>
       <c r="G1164" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -54782,8 +54378,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1165" t="inlineStr"/>
-      <c r="G1165" t="inlineStr"/>
       <c r="H1165" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54827,8 +54421,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1166" t="inlineStr"/>
-      <c r="G1166" t="inlineStr"/>
       <c r="H1166" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54872,8 +54464,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1167" t="inlineStr"/>
-      <c r="G1167" t="inlineStr"/>
       <c r="H1167" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54917,8 +54507,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1168" t="inlineStr"/>
-      <c r="G1168" t="inlineStr"/>
       <c r="H1168" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -54962,8 +54550,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1169" t="inlineStr"/>
-      <c r="G1169" t="inlineStr"/>
       <c r="H1169" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -55007,8 +54593,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1170" t="inlineStr"/>
-      <c r="G1170" t="inlineStr"/>
       <c r="H1170" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -55052,8 +54636,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1171" t="inlineStr"/>
-      <c r="G1171" t="inlineStr"/>
       <c r="H1171" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -55097,7 +54679,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1172" t="inlineStr"/>
       <c r="G1172" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55146,7 +54727,6 @@
           <t>Beauvais, Hauts-de-France, France</t>
         </is>
       </c>
-      <c r="F1173" t="inlineStr"/>
       <c r="G1173" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55195,8 +54775,6 @@
           <t>Châtillon</t>
         </is>
       </c>
-      <c r="F1174" t="inlineStr"/>
-      <c r="G1174" t="inlineStr"/>
       <c r="H1174" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -55240,7 +54818,6 @@
           <t>Chaville, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1175" t="inlineStr"/>
       <c r="G1175" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55289,7 +54866,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1176" t="inlineStr"/>
       <c r="G1176" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55338,7 +54914,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1177" t="inlineStr"/>
       <c r="G1177" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55387,7 +54962,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1178" t="inlineStr"/>
       <c r="G1178" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55436,8 +55010,6 @@
           <t>Sèvres</t>
         </is>
       </c>
-      <c r="F1179" t="inlineStr"/>
-      <c r="G1179" t="inlineStr"/>
       <c r="H1179" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -55481,7 +55053,6 @@
           <t>Compiègne, Hauts-de-France, France</t>
         </is>
       </c>
-      <c r="F1180" t="inlineStr"/>
       <c r="G1180" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55530,8 +55101,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1181" t="inlineStr"/>
-      <c r="G1181" t="inlineStr"/>
       <c r="H1181" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -55575,8 +55144,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1182" t="inlineStr"/>
-      <c r="G1182" t="inlineStr"/>
       <c r="H1182" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -55620,7 +55187,6 @@
           <t>La Celle-Saint-Cloud, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1183" t="inlineStr"/>
       <c r="G1183" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55669,7 +55235,6 @@
           <t>Dreux, Centre-Val de Loire, France</t>
         </is>
       </c>
-      <c r="F1184" t="inlineStr"/>
       <c r="G1184" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55718,7 +55283,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1185" t="inlineStr"/>
       <c r="G1185" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -55767,7 +55331,6 @@
           <t>La Frette-sur-Seine, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1186" t="inlineStr"/>
       <c r="G1186" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55816,7 +55379,6 @@
           <t>La Frette-sur-Seine, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1187" t="inlineStr"/>
       <c r="G1187" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55865,7 +55427,6 @@
           <t>La Frette-sur-Seine, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1188" t="inlineStr"/>
       <c r="G1188" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55914,7 +55475,6 @@
           <t>St.-Cloud, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1189" t="inlineStr"/>
       <c r="G1189" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -55963,7 +55523,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1190" t="inlineStr"/>
       <c r="G1190" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -56012,7 +55571,6 @@
           <t>Courbevoie</t>
         </is>
       </c>
-      <c r="F1191" t="inlineStr"/>
       <c r="G1191" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -56061,8 +55619,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1192" t="inlineStr"/>
-      <c r="G1192" t="inlineStr"/>
       <c r="H1192" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56106,7 +55662,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1193" t="inlineStr"/>
       <c r="G1193" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -56155,8 +55710,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1194" t="inlineStr"/>
-      <c r="G1194" t="inlineStr"/>
       <c r="H1194" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56200,8 +55753,6 @@
           <t>Saint-Denis</t>
         </is>
       </c>
-      <c r="F1195" t="inlineStr"/>
-      <c r="G1195" t="inlineStr"/>
       <c r="H1195" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56245,8 +55796,6 @@
           <t>Créteil</t>
         </is>
       </c>
-      <c r="F1196" t="inlineStr"/>
-      <c r="G1196" t="inlineStr"/>
       <c r="H1196" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56290,8 +55839,6 @@
           <t>Asnières-sur-Seine</t>
         </is>
       </c>
-      <c r="F1197" t="inlineStr"/>
-      <c r="G1197" t="inlineStr"/>
       <c r="H1197" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56335,8 +55882,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1198" t="inlineStr"/>
-      <c r="G1198" t="inlineStr"/>
       <c r="H1198" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56380,8 +55925,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1199" t="inlineStr"/>
-      <c r="G1199" t="inlineStr"/>
       <c r="H1199" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56425,8 +55968,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1200" t="inlineStr"/>
-      <c r="G1200" t="inlineStr"/>
       <c r="H1200" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56470,8 +56011,6 @@
           <t>Buc</t>
         </is>
       </c>
-      <c r="F1201" t="inlineStr"/>
-      <c r="G1201" t="inlineStr"/>
       <c r="H1201" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56515,8 +56054,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1202" t="inlineStr"/>
-      <c r="G1202" t="inlineStr"/>
       <c r="H1202" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56560,8 +56097,6 @@
           <t>Massy</t>
         </is>
       </c>
-      <c r="F1203" t="inlineStr"/>
-      <c r="G1203" t="inlineStr"/>
       <c r="H1203" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56605,8 +56140,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1204" t="inlineStr"/>
-      <c r="G1204" t="inlineStr"/>
       <c r="H1204" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56650,8 +56183,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1205" t="inlineStr"/>
-      <c r="G1205" t="inlineStr"/>
       <c r="H1205" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56695,8 +56226,6 @@
           <t>Évry</t>
         </is>
       </c>
-      <c r="F1206" t="inlineStr"/>
-      <c r="G1206" t="inlineStr"/>
       <c r="H1206" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56740,8 +56269,6 @@
           <t>Clichy</t>
         </is>
       </c>
-      <c r="F1207" t="inlineStr"/>
-      <c r="G1207" t="inlineStr"/>
       <c r="H1207" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56785,8 +56312,6 @@
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="F1208" t="inlineStr"/>
-      <c r="G1208" t="inlineStr"/>
       <c r="H1208" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56830,8 +56355,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1209" t="inlineStr"/>
-      <c r="G1209" t="inlineStr"/>
       <c r="H1209" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56875,8 +56398,6 @@
           <t>Sceaux</t>
         </is>
       </c>
-      <c r="F1210" t="inlineStr"/>
-      <c r="G1210" t="inlineStr"/>
       <c r="H1210" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -56920,7 +56441,6 @@
           <t>Beauvais, Hauts-de-France, France</t>
         </is>
       </c>
-      <c r="F1211" t="inlineStr"/>
       <c r="G1211" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -56969,7 +56489,6 @@
           <t>Mainvilliers, Centre-Val de Loire, France</t>
         </is>
       </c>
-      <c r="F1212" t="inlineStr"/>
       <c r="G1212" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57018,8 +56537,6 @@
           <t>Saint-Denis</t>
         </is>
       </c>
-      <c r="F1213" t="inlineStr"/>
-      <c r="G1213" t="inlineStr"/>
       <c r="H1213" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -57063,7 +56580,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1214" t="inlineStr"/>
       <c r="G1214" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57112,7 +56628,6 @@
           <t>Vémars, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1215" t="inlineStr"/>
       <c r="G1215" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57161,7 +56676,6 @@
           <t>Rennes</t>
         </is>
       </c>
-      <c r="F1216" t="inlineStr"/>
       <c r="G1216" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -57210,7 +56724,6 @@
           <t>Aix-en-Provence</t>
         </is>
       </c>
-      <c r="F1217" t="inlineStr"/>
       <c r="G1217" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -57259,7 +56772,6 @@
           <t>Chevilly-Larue, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1218" t="inlineStr"/>
       <c r="G1218" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57308,7 +56820,6 @@
           <t>Villebon-sur-Yvette, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1219" t="inlineStr"/>
       <c r="G1219" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57357,7 +56868,6 @@
           <t>Us, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1220" t="inlineStr"/>
       <c r="G1220" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57406,7 +56916,6 @@
           <t>Étrépagny, Normandy, France</t>
         </is>
       </c>
-      <c r="F1221" t="inlineStr"/>
       <c r="G1221" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57455,7 +56964,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1222" t="inlineStr"/>
       <c r="G1222" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57504,7 +57012,6 @@
           <t>Marseille</t>
         </is>
       </c>
-      <c r="F1223" t="inlineStr"/>
       <c r="G1223" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -57553,7 +57060,6 @@
           <t>Marseille</t>
         </is>
       </c>
-      <c r="F1224" t="inlineStr"/>
       <c r="G1224" t="inlineStr">
         <is>
           <t>full_time</t>
@@ -57602,7 +57108,6 @@
           <t>Bondoufle, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1225" t="inlineStr"/>
       <c r="G1225" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57651,7 +57156,6 @@
           <t>Creil, Hauts-de-France, France</t>
         </is>
       </c>
-      <c r="F1226" t="inlineStr"/>
       <c r="G1226" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57700,7 +57204,6 @@
           <t>Creil, Hauts-de-France, France</t>
         </is>
       </c>
-      <c r="F1227" t="inlineStr"/>
       <c r="G1227" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57749,7 +57252,6 @@
           <t>Creil, Hauts-de-France, France</t>
         </is>
       </c>
-      <c r="F1228" t="inlineStr"/>
       <c r="G1228" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57798,7 +57300,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1229" t="inlineStr"/>
       <c r="G1229" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57847,7 +57348,6 @@
           <t>Sainte-Geneviève, Hauts-de-France, France</t>
         </is>
       </c>
-      <c r="F1230" t="inlineStr"/>
       <c r="G1230" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57896,7 +57396,6 @@
           <t>Brétigny-sur-Orge, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1231" t="inlineStr"/>
       <c r="G1231" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57945,7 +57444,6 @@
           <t>Maurepas, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1232" t="inlineStr"/>
       <c r="G1232" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -57994,7 +57492,6 @@
           <t>Bus-Saint-Rémy, Normandy, France</t>
         </is>
       </c>
-      <c r="F1233" t="inlineStr"/>
       <c r="G1233" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58043,7 +57540,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1234" t="inlineStr"/>
       <c r="G1234" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58092,7 +57588,6 @@
           <t>Voisins-le-Bretonneux, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1235" t="inlineStr"/>
       <c r="G1235" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58141,7 +57636,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1236" t="inlineStr"/>
       <c r="G1236" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58190,8 +57684,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1237" t="inlineStr"/>
-      <c r="G1237" t="inlineStr"/>
       <c r="H1237" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -58235,8 +57727,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1238" t="inlineStr"/>
-      <c r="G1238" t="inlineStr"/>
       <c r="H1238" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -58280,7 +57770,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1239" t="inlineStr"/>
       <c r="G1239" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58329,7 +57818,6 @@
           <t>Bus-Saint-Rémy, Normandy, France</t>
         </is>
       </c>
-      <c r="F1240" t="inlineStr"/>
       <c r="G1240" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58378,7 +57866,6 @@
           <t>St.-Arnoult-en-Yvelines, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1241" t="inlineStr"/>
       <c r="G1241" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58427,7 +57914,6 @@
           <t>Levallois-Perret, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1242" t="inlineStr"/>
       <c r="G1242" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58476,7 +57962,6 @@
           <t>Dreux, Centre-Val de Loire, France</t>
         </is>
       </c>
-      <c r="F1243" t="inlineStr"/>
       <c r="G1243" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58525,7 +58010,6 @@
           <t>Dreux, Centre-Val de Loire, France</t>
         </is>
       </c>
-      <c r="F1244" t="inlineStr"/>
       <c r="G1244" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58574,8 +58058,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1245" t="inlineStr"/>
-      <c r="G1245" t="inlineStr"/>
       <c r="H1245" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -58619,7 +58101,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1246" t="inlineStr"/>
       <c r="G1246" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58668,7 +58149,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1247" t="inlineStr"/>
       <c r="G1247" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58717,7 +58197,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1248" t="inlineStr"/>
       <c r="G1248" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58766,7 +58245,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1249" t="inlineStr"/>
       <c r="G1249" t="inlineStr">
         <is>
           <t>Other</t>
@@ -58815,7 +58293,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1250" t="inlineStr"/>
       <c r="G1250" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -58864,8 +58341,6 @@
           <t>Puteaux</t>
         </is>
       </c>
-      <c r="F1251" t="inlineStr"/>
-      <c r="G1251" t="inlineStr"/>
       <c r="H1251" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -58909,8 +58384,6 @@
           <t>Sèvres</t>
         </is>
       </c>
-      <c r="F1252" t="inlineStr"/>
-      <c r="G1252" t="inlineStr"/>
       <c r="H1252" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -58954,7 +58427,6 @@
           <t>Chartres, Centre-Val de Loire, France</t>
         </is>
       </c>
-      <c r="F1253" t="inlineStr"/>
       <c r="G1253" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -59003,7 +58475,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1254" t="inlineStr"/>
       <c r="G1254" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -59052,8 +58523,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1255" t="inlineStr"/>
-      <c r="G1255" t="inlineStr"/>
       <c r="H1255" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -59097,7 +58566,6 @@
           <t>Conflans-Ste.-Honorine, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1256" t="inlineStr"/>
       <c r="G1256" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -59146,7 +58614,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1257" t="inlineStr"/>
       <c r="G1257" t="inlineStr">
         <is>
           <t>Other</t>
@@ -59195,8 +58662,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1258" t="inlineStr"/>
-      <c r="G1258" t="inlineStr"/>
       <c r="H1258" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -59240,7 +58705,6 @@
           <t>Paris, Île-de-France, France</t>
         </is>
       </c>
-      <c r="F1259" t="inlineStr"/>
       <c r="G1259" t="inlineStr">
         <is>
           <t>Full-time</t>
@@ -59289,8 +58753,6 @@
           <t>Paris</t>
         </is>
       </c>
-      <c r="F1260" t="inlineStr"/>
-      <c r="G1260" t="inlineStr"/>
       <c r="H1260" t="inlineStr">
         <is>
           <t>Not disclosed</t>
@@ -59307,6 +58769,2841 @@
         </is>
       </c>
       <c r="M1260" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="B1261" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Product Manager Digital Assets H/F</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Euronext</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1261" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/euronext-177879.html</t>
+        </is>
+      </c>
+      <c r="L1261" t="inlineStr">
+        <is>
+          <t>Capital-markets domain overlap (custody/settlement) mirrors Sophis/Finastra background; Euronext is a top target employer | Gap: No AI/ML component and seniority unclear vs his 15+yr Director-level track record</t>
+        </is>
+      </c>
+      <c r="M1261" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="B1262" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Estreem - Product Manager Issuing H/F</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>BNP Paribas</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1262" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/bnp-paribas-3597.html</t>
+        </is>
+      </c>
+      <c r="L1262" t="inlineStr">
+        <is>
+          <t>Payments/fintech financial domain fits, and BNP Paribas/BPCE is a core target institution | Gap: IC-level payments PM scope, no AI angle, below his Director/Principal seniority</t>
+        </is>
+      </c>
+      <c r="M1262" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="B1263" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Payment Product Manager - Banking Platform H/F</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Swan.io</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1263" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/swanio-211191.html</t>
+        </is>
+      </c>
+      <c r="L1263" t="inlineStr">
+        <is>
+          <t>Named target fintech (Swan) in embedded banking/payments, financial-services core | Gap: No AI/ML ownership and role reads as mid-level IC PM, not Lead/Director</t>
+        </is>
+      </c>
+      <c r="M1263" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="B1264" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Sr Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Dataiku</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1264" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/dataiku-107602.html</t>
+        </is>
+      </c>
+      <c r="L1264" t="inlineStr">
+        <is>
+          <t>Dataiku is his top target AI platform and he holds two Dataiku GenAI/Designer certs plus RAG/agentic training | Gap: Not a financial-services company, so domain overlap is AI-only rather than fin+AI combined</t>
+        </is>
+      </c>
+      <c r="M1264" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="B1265" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Senior Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Greenly</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1265" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010244405335</t>
+        </is>
+      </c>
+      <c r="L1265" t="inlineStr">
+        <is>
+          <t>Senior-level marketing/product title matches seniority range | Gap: Carbon-accounting sector has no financial-services or AI-product overlap, and it's a marketing not core PM role</t>
+        </is>
+      </c>
+      <c r="M1265" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="B1266" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Technical Product Manager – Navigation Inertielle &amp; Systèmes maritimes (H/F)</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>SBG Systems</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1266" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010244415177</t>
+        </is>
+      </c>
+      <c r="L1266" t="inlineStr">
+        <is>
+          <t>Some transferable product-ownership process experience | Gap: Defense/marine navigation hardware sector is entirely unrelated to financial services or AI product work</t>
+        </is>
+      </c>
+      <c r="M1266" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="B1267" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Product Manager - Noa F/H</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Padoa</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1267" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010244726258</t>
+        </is>
+      </c>
+      <c r="L1267" t="inlineStr">
+        <is>
+          <t>Product ownership process skills transfer | Gap: Health-tech scale-up outside financial services, no AI focus, unclear seniority fit</t>
+        </is>
+      </c>
+      <c r="M1267" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="B1268" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Product Owner Cartographie (F/H)</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1268" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/sii/jobs/product-owner-cartographie-f-h_le-mans</t>
+        </is>
+      </c>
+      <c r="L1268" t="inlineStr">
+        <is>
+          <t>Basic Product Owner process skills transfer | Gap: ESN/consulting staffing role, mapping domain, junior-mid scope with no fin/AI relevance</t>
+        </is>
+      </c>
+      <c r="M1268" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="B1269" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>CDI  - Data Product Manager Analytics &amp; AI - Retail (H/F)</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1269" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/hermes/jobs/cdi-data-product-manager-analytics-ai-retail-h-f_pantin_HERMS_dQq8PPd</t>
+        </is>
+      </c>
+      <c r="L1269" t="inlineStr">
+        <is>
+          <t>Explicit Analytics &amp; AI data product ownership aligns with his Opensee/Dataiku AI-data pipeline experience | Gap: Luxury retail sector, not financial services, and seniority level for the role is unstated/likely mid</t>
+        </is>
+      </c>
+      <c r="M1269" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="B1270" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>CDI - Data Product Manager - AI Platform (H/F)</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1270" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/hermes/jobs/cdi-data-product-manager-ai-platform-h-f_pantin_HERMS_VGz5y12</t>
+        </is>
+      </c>
+      <c r="L1270" t="inlineStr">
+        <is>
+          <t>AI platform/infrastructure product ownership directly matches his AI-agentic and data-platform certifications | Gap: Not a financial institution and the posting gives no signal of Lead/Director-level scope</t>
+        </is>
+      </c>
+      <c r="M1270" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="B1271" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Operations Security Product Manager</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1271" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/pernod-ricard/jobs/operations-security-product-manager_paris</t>
+        </is>
+      </c>
+      <c r="L1271" t="inlineStr">
+        <is>
+          <t>Strategic roadmap-steering scope suggests a senior-level role | Gap: Spirits/beverage sector, security-ops domain has no financial-services or AI overlap</t>
+        </is>
+      </c>
+      <c r="M1271" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="B1272" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Lifecycle &amp; Quality Product Manager</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1272" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/pernod-ricard/jobs/r-d-product-lifecycle-quality-product-manager_paris</t>
+        </is>
+      </c>
+      <c r="L1272" t="inlineStr">
+        <is>
+          <t>Strategic vision/roadmap ownership signals a senior scope matching his experience level | Gap: Wine &amp; spirits R&amp;D/lifecycle domain is unrelated to financial services or AI products</t>
+        </is>
+      </c>
+      <c r="M1272" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="B1273" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Product Owner (H/F)</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1273" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/meritis/jobs/product-owner-h-f_aix-en-provence</t>
+        </is>
+      </c>
+      <c r="L1273" t="inlineStr">
+        <is>
+          <t>Generic Product Owner backlog/roadmap skills transfer | Gap: Digital-transformation consulting (ESN) generalist role, 5yr-level seniority well below his profile, no fin/AI angle</t>
+        </is>
+      </c>
+      <c r="M1273" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="B1274" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Technical Product Owner (F/H)</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1274" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/thales/jobs/product-owner-f-h_gemenos_THALE_0Kz6L2d</t>
+        </is>
+      </c>
+      <c r="L1274" t="inlineStr">
+        <is>
+          <t>Payment platform product ownership is financial-services adjacent and close to his payments/trading software background | Gap: Technical Product Owner is an IC-level role well below his Principal/Director seniority, and it's based outside Paris (La Ciotat)</t>
+        </is>
+      </c>
+      <c r="M1274" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="B1275" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Founding Product</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1275" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/the-product-crew/jobs/python-developer_paris</t>
+        </is>
+      </c>
+      <c r="L1275" t="inlineStr">
+        <is>
+          <t>Founding PM freedom could suit his freelance/entrepreneurial recent chapter | Gap: Vague third-party listing (The Product Crew) with no named employer, sector, or seniority signal to evaluate fit against</t>
+        </is>
+      </c>
+      <c r="M1275" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="B1276" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Product Recruiter - Product, Design, Ops </t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1276" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/the-product-crew/jobs/product-recruiter-account-manager-h-f-full-remote-possible</t>
+        </is>
+      </c>
+      <c r="L1276" t="inlineStr">
+        <is>
+          <t>None - this is a recruiting/talent role, not a product management position | Gap: Not a PM job at all; mismatched function despite the 'Product' branding</t>
+        </is>
+      </c>
+      <c r="M1276" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="B1277" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1277" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/the-product-crew/jobs/product-manager-senior-pm-lead-pm_paris</t>
+        </is>
+      </c>
+      <c r="L1277" t="inlineStr">
+        <is>
+          <t>Generic PM title keeps door open to a fin/AI-adjacent opportunity | Gap: Faceless third-party listing (The Product Crew) with no company, sector, or seniority detail to assess</t>
+        </is>
+      </c>
+      <c r="M1277" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="B1278" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Head of Product</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1278" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/the-product-crew/jobs/head-of-product-cpo_paris</t>
+        </is>
+      </c>
+      <c r="L1278" t="inlineStr">
+        <is>
+          <t>Head of Product level matches his 15+yr seniority expectations | Gap: Anonymous listing via recruiter aggregator with no company or sector named, so domain/AI fit is unknown</t>
+        </is>
+      </c>
+      <c r="M1278" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="B1279" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Head of Product Management &amp; Marketing F/H </t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1279" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/safran/jobs/head-of-product-management-marketing-f-h_plaisir</t>
+        </is>
+      </c>
+      <c r="L1279" t="inlineStr">
+        <is>
+          <t>Head-of-Product seniority with team management matches his leadership level | Gap: Aerospace aftermarket marketing sector has no financial-services or AI-product overlap</t>
+        </is>
+      </c>
+      <c r="M1279" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="B1280" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Lead Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1280" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/hubvisory/jobs/lead-product-manager-h-f_lille_HUBVI_qVJkMLq</t>
+        </is>
+      </c>
+      <c r="L1280" t="inlineStr">
+        <is>
+          <t>Lead Product Manager seniority and consulting/workshop-driven client engagement echo his Finastra advisory experience | Gap: Retail-sector consulting engagement, no financial-services core or AI component</t>
+        </is>
+      </c>
+      <c r="M1280" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="B1281" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Product Manager Core Navigation Experience (F/M)</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1281" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/betclic/jobs/product-manager-core-navigation-experience-f-m_bordeaux</t>
+        </is>
+      </c>
+      <c r="L1281" t="inlineStr">
+        <is>
+          <t>Product management process experience transfers to any consumer digital product | Gap: Sports-betting/gambling sector is unrelated to financial services and has no AI product angle</t>
+        </is>
+      </c>
+      <c r="M1281" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="B1282" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Sales Executive &amp; Product Manager</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>(unnamed - via WTTJ listing)</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1282" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/galadrim/jobs/cdi-business-developer-chef-fe-de-projet-digital_paris</t>
+        </is>
+      </c>
+      <c r="L1282" t="inlineStr">
+        <is>
+          <t>Some go-to-market/roadmap exposure could transfer loosely | Gap: Hybrid sales+PM generalist role at a small digital agency, junior scope, no financial-services or AI relevance</t>
+        </is>
+      </c>
+      <c r="M1282" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="B1283" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Product Design Lead</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Mendo</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1283" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/mendo-1/jobs/product-design-lead_paris_MENDO_JZqOY66</t>
+        </is>
+      </c>
+      <c r="L1283" t="inlineStr">
+        <is>
+          <t>GenAI enterprise platform aligns with his AI product interest and certifications. | Gap: This is a design-team leadership role, not product management, and CV has no design-team management experience.</t>
+        </is>
+      </c>
+      <c r="M1283" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="B1284" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - Agentic &amp; AI Automation</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Believe</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1284" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/believe-digital/jobs/senior-product-manager-agentic-ai-automation_paris</t>
+        </is>
+      </c>
+      <c r="L1284" t="inlineStr">
+        <is>
+          <t>Agentic AI ownership matches his crewAI/LangChain certifications and hands-on agentic PoC work. | Gap: Music industry has zero overlap with his financial services domain expertise.</t>
+        </is>
+      </c>
+      <c r="M1284" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="B1285" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Fleet Manager - Product Owner Borne - Île-De-France H/F</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>PROJECTTECH ENGINEERING</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1285" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/projecttech-engineering-179681.html</t>
+        </is>
+      </c>
+      <c r="L1285" t="inlineStr">
+        <is>
+          <t>General product ownership/operations coordination is a transferable skill. | Gap: EV charging infrastructure has no financial or AI relevance and no seniority signal for a 15+yr profile.</t>
+        </is>
+      </c>
+      <c r="M1285" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="B1286" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Global Product Marketing Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Edflex</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1286" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/edflex-105721.html</t>
+        </is>
+      </c>
+      <c r="L1286" t="inlineStr">
+        <is>
+          <t>Global-scope product role fits his cross-region (EMEA/Americas) experience at Finastra. | Gap: E-learning/training sector and marketing focus have no ties to finance or AI product ownership.</t>
+        </is>
+      </c>
+      <c r="M1286" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="B1287" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Senior Product Marketing Manager - Paris H/F</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Shippeo</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1287" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/shippeo-93016.html</t>
+        </is>
+      </c>
+      <c r="L1287" t="inlineStr">
+        <is>
+          <t>Predictive-AI supply-chain SaaS gives some AI product exposure, echoing his Opensee SaaS analytics background. | Gap: Supply chain/logistics sector is unrelated to his financial services focus and role is marketing not core PM.</t>
+        </is>
+      </c>
+      <c r="M1287" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="B1288" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Product Owner E-Commerce H/F</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Balmain</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1288" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/balmain-179769.html</t>
+        </is>
+      </c>
+      <c r="L1288" t="inlineStr">
+        <is>
+          <t>Product ownership discipline transfers generically across industries. | Gap: Luxury fashion e-commerce is entirely unrelated to finance/AI and likely below his seniority level.</t>
+        </is>
+      </c>
+      <c r="M1288" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="B1289" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Responsable du pôle Product Management - Secteur Energie F/H</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Agregio Solutions</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1289" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/edf/jobs/responsable-du-pole-product-management-secteur-energie-f-h_la-defense</t>
+        </is>
+      </c>
+      <c r="L1289" t="inlineStr">
+        <is>
+          <t>Head-of-product-pole scope managing a 10-person team matches his 15+ yrs leadership level. | Gap: Energy transition sector has no financial services or AI product overlap.</t>
+        </is>
+      </c>
+      <c r="M1289" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="B1290" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Senior Product Designer</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Alma</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1290" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/alma/jobs/senior-product-designer_paris</t>
+        </is>
+      </c>
+      <c r="L1290" t="inlineStr">
+        <is>
+          <t>Alma is a BNPL fintech, giving direct financial-sector relevance close to his domain. | Gap: Role is Senior Product Designer, not Product Manager — a discipline mismatch versus his PM track record.</t>
+        </is>
+      </c>
+      <c r="M1290" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="B1291" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>FinOps Lead Technology &amp; Product</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Sekoia</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1291" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/sekoia/jobs/finops-lead-technology-product</t>
+        </is>
+      </c>
+      <c r="L1291" t="inlineStr">
+        <is>
+          <t>Lead-level scope working with CFO/CTPO fits his budget-ownership and executive-stakeholder experience. | Gap: FinOps/cloud cost governance in cybersecurity is not a product management role and not AI-centric.</t>
+        </is>
+      </c>
+      <c r="M1291" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="B1292" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Senior Product Manager ai &amp; Internal Tooling Implicity Is Hiring H/F</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>implicity</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1292" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/implicity-105999.html</t>
+        </is>
+      </c>
+      <c r="L1292" t="inlineStr">
+        <is>
+          <t>AI-driven SaaS platform PM role matches his hands-on AI PoC and product-led SaaS experience at Opensee. | Gap: Cardiology/healthcare SaaS is unrelated to his financial services domain expertise.</t>
+        </is>
+      </c>
+      <c r="M1292" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="B1293" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Product Manager Data &amp; ai Platform H/F</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Wold</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1293" t="inlineStr">
+        <is>
+          <t>Data &amp; AI platform ownership (backlog, roadmap, technical teams) closely mirrors his Opensee ETL/NiFi/OpenMetadata product ownership. | Gap: Role sits alongside a Product Lead rather than leading, and the unnamed 'grand groupe' client/sector isn't confirmed financial.</t>
+        </is>
+      </c>
+      <c r="M1293" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="B1294" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Product Manager Digital H/F</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>GBH</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1294" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/gbh-168838.html</t>
+        </is>
+      </c>
+      <c r="L1294" t="inlineStr">
+        <is>
+          <t>Digital transformation PM role within an internal IT organization is a transferable structure. | Gap: Retail/automotive/industry conglomerate has no financial services or AI-centric relevance.</t>
+        </is>
+      </c>
+      <c r="M1294" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="B1295" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Founding Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Team.is</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1295" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/teamis-101426.html</t>
+        </is>
+      </c>
+      <c r="L1295" t="inlineStr">
+        <is>
+          <t>AI-powered recruiting angle echoes his own AI recruiting-matching PoC for TradeValue/Woon. | Gap: Posting is a recruitment agency's generic listing with no clear financial sector or confirmed AI product ownership for the actual role.</t>
+        </is>
+      </c>
+      <c r="M1295" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="B1296" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Product Manager E-Commerce H/F</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Audensiel Technologies</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1296" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/audensiel-technologies-76493.html</t>
+        </is>
+      </c>
+      <c r="L1296" t="inlineStr">
+        <is>
+          <t>High-traffic digital product delivery experience is broadly transferable. | Gap: ESN/consulting staffing model for e-commerce PDP work has no financial or AI product tie.</t>
+        </is>
+      </c>
+      <c r="M1296" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="B1297" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Assistant Product Manager Motorcycle H/F</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Bridgestone</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1297" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/bridgestone-123677.html</t>
+        </is>
+      </c>
+      <c r="L1297" t="inlineStr">
+        <is>
+          <t>None material — general industrial product management exposure only. | Gap: Assistant-level junior title is a severe seniority mismatch for 15+ yrs experience, plus tires/manufacturing is unrelated to finance/AI.</t>
+        </is>
+      </c>
+      <c r="M1297" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="B1298" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Data Product Owner - Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>SOMA</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1298" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/soma-group-160404.html</t>
+        </is>
+      </c>
+      <c r="L1298" t="inlineStr">
+        <is>
+          <t>Data &amp; AI-in-production consultancy work aligns strongly with his Dataiku/NiFi/data-platform certifications and experience. | Gap: Consulting delivery model for large accounts (unnamed sector) is not confirmed financial services.</t>
+        </is>
+      </c>
+      <c r="M1298" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="B1299" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Chef de Produit Technique Sénior - CDI - Paris H/F</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Manpower France</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1299" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/manpower-94171.html</t>
+        </is>
+      </c>
+      <c r="L1299" t="inlineStr">
+        <is>
+          <t>Senior/strategic technical product category role fits his seniority; a named recruiting cabinet (Manpower) is present. | Gap: Home equipment/habitat industry has no financial or AI product relevance.</t>
+        </is>
+      </c>
+      <c r="M1299" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="B1300" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Keewe</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1300" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/keewe-210509.html</t>
+        </is>
+      </c>
+      <c r="L1300" t="inlineStr">
+        <is>
+          <t>Finance/compliance-heavy product scoping described in the posting maps directly to his financial risk-platform and regulatory background. | Gap: Keewe is a growth-stage fintech, not a named large institution, and the role isn't explicitly AI-centric.</t>
+        </is>
+      </c>
+      <c r="M1300" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="B1301" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Product Manager Média H/F</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>5 Degrés</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1301" t="inlineStr">
+        <is>
+          <t>Consultancy serves banque/assurance clients among sectors, giving indirect financial services exposure. | Gap: This specific assignment is Média, not banking/insurance, and no AI product angle is mentioned.</t>
+        </is>
+      </c>
+      <c r="M1301" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="B1302" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Product Builder</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Galadrim</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1302" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/galadrim/jobs/product-builder</t>
+        </is>
+      </c>
+      <c r="L1302" t="inlineStr">
+        <is>
+          <t>Tech/AI agency work gives some AI product exposure aligned to his recent AI upskilling. | Gap: Junior 'Product Builder' role reporting to a Lead is a major seniority mismatch for 15+ yrs experience.</t>
+        </is>
+      </c>
+      <c r="M1302" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="B1303" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Product Manager - Catalog H/F</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Joko</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1303" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/joko-93011.html</t>
+        </is>
+      </c>
+      <c r="L1303" t="inlineStr">
+        <is>
+          <t>Cashback/financial-perks app with an AI shopping assistant gives partial fintech and AI relevance. | Gap: Catalog/merchant-data PM scope is mid-level IC work, below his director/lead-level track record.</t>
+        </is>
+      </c>
+      <c r="M1303" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="B1304" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Product Manager Data H/F</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Yunik</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1304" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Lead role in a large regulated group (Snowflake/Power BI, industrialization at scale) closely matches his Opensee data-platform ownership and regulatory (ISO27001/HSBC) experience. | Gap: Client sector/name isn't disclosed as a named target financial institution, and explicit AI ownership isn't confirmed.</t>
+        </is>
+      </c>
+      <c r="M1304" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="B1305" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Product Owner H/F</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Groupe Alliance</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1305" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/groupe-alliance-94476.html</t>
+        </is>
+      </c>
+      <c r="L1305" t="inlineStr">
+        <is>
+          <t>ESN staffing covers banking/finance/insurance clients, matching sector experience | Gap: Generic ESN placement, no seniority/AI specifics, no named target employer</t>
+        </is>
+      </c>
+      <c r="M1305" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="B1306" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Product Owner Data Finance H/F</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Wold</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1306" t="inlineStr">
+        <is>
+          <t>Direct Finance-department data product ownership mirrors Opensee/Natixis background | Gap: Mid-level PO scope, no AI/ML angle, unknown/non-target employer</t>
+        </is>
+      </c>
+      <c r="M1306" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="B1307" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Head of Data Product – Niveau : Manager / Senior Manager</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="B1308" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Lead AI Product Manager - Agentic &amp; ML</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="B1309" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Product Manager Firewall H/F</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Stormshield</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1309" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/stormshield-134245.html</t>
+        </is>
+      </c>
+      <c r="L1309" t="inlineStr">
+        <is>
+          <t>Enterprise B2B security product management transfers general PM discipline | Gap: No finance or AI relevance; firewall/cybersecurity is an unrelated technical domain</t>
+        </is>
+      </c>
+      <c r="M1309" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="B1310" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Head Of Product Transformation - Consultant·e en Organisation Produit H/F</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>Thiga</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1310" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/thiga-108505.html</t>
+        </is>
+      </c>
+      <c r="L1310" t="inlineStr">
+        <is>
+          <t>Head-level transformation consulting for grands comptes matches 15+yr program leadership and AI-impact audits | Gap: Product-org consulting generalist, not finance-sector-specific, employer not on target list</t>
+        </is>
+      </c>
+      <c r="M1310" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="B1311" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Product Manager Ux Orchestration H/F</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Sparteo</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1311" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/sparteo-210860.html</t>
+        </is>
+      </c>
+      <c r="L1311" t="inlineStr">
+        <is>
+          <t>AI-powered data-driven platform gives some AI product overlap | Gap: Adtech sector unrelated to finance, mid-level PM title below director-level experience</t>
+        </is>
+      </c>
+      <c r="M1311" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="B1312" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Responsable Produit Contrôle de Température H/F</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Urvika</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1312" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/urvika-91620.html</t>
+        </is>
+      </c>
+      <c r="L1312" t="inlineStr">
+        <is>
+          <t>None meaningful — generic product-strategy transferable skills only | Gap: HVAC/hardware product role entirely outside finance, AI, and software domain</t>
+        </is>
+      </c>
+      <c r="M1312" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="B1313" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Senior Product Manager W - M - Data &amp; Connectivity H/F</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Splio</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1313" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/splio-110255.html</t>
+        </is>
+      </c>
+      <c r="L1313" t="inlineStr">
+        <is>
+          <t>AI-first CRM/data platform with agentic-AI direction matches Dataiku/agentic AI credentials | Gap: Martech/CRM sector, not financial services, seniority is Senior PM not Head/Director</t>
+        </is>
+      </c>
+      <c r="M1313" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="B1314" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Payhawk Limited</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1314" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010239174917</t>
+        </is>
+      </c>
+      <c r="L1314" t="inlineStr">
+        <is>
+          <t>Fintech spend-management company gives adjacent financial-sector product context | Gap: Role is product marketing not product management, function mismatch with CV background</t>
+        </is>
+      </c>
+      <c r="M1314" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="B1315" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Product Engineer Python - React - Nextjs H/F</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Zenior</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1315" t="inlineStr">
+        <is>
+          <t>Company applies AI/automation to a real-world sector | Gap: This is a hands-on software engineering role, not a product management position</t>
+        </is>
+      </c>
+      <c r="M1315" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="B1316" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Head Of Product Payment H/F</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Malt</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1316" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/malt-116199.html</t>
+        </is>
+      </c>
+      <c r="L1316" t="inlineStr">
+        <is>
+          <t>Head-of-Product payments leadership aligns with seniority and financial/transaction product experience | Gap: Freelance marketplace sector, not a core financial institution, no explicit AI scope</t>
+        </is>
+      </c>
+      <c r="M1316" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="B1317" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Product Manager IA H/F</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>5 Degrés</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1317" t="inlineStr">
+        <is>
+          <t>AI product vision/strategy role plays directly to 2025 AI certifications and multidisciplinary team leadership | Gap: ESN client-staffing model, seniority level unclear/likely mid, no finance-sector anchor</t>
+        </is>
+      </c>
+      <c r="M1317" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="B1318" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - M - Hublo H/F</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>Hublot</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1318" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/hublot-107729.html</t>
+        </is>
+      </c>
+      <c r="L1318" t="inlineStr">
+        <is>
+          <t>Senior PM title matches seniority band for a scaled SaaS platform | Gap: Healthcare HR-staffing SaaS is unrelated to finance or AI product focus</t>
+        </is>
+      </c>
+      <c r="M1318" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="B1319" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Product Manager Senior Mobile - CDI H/F</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>SprintMob</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1319" t="inlineStr">
+        <is>
+          <t>Senior PM role for a growing fintech client's mobile product plays to financial-sector product ownership | Gap: Consumer mobile B2C scope with no AI dimension, agency/staffing intermediary structure</t>
+        </is>
+      </c>
+      <c r="M1319" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="B1320" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Product Owner H/F</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>Whub</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1320" t="inlineStr">
+        <is>
+          <t>Digital subscription platform ownership shows some transferable SaaS product skills | Gap: No finance, AI, or senior-leadership scope; generic mid-level PO role</t>
+        </is>
+      </c>
+      <c r="M1320" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="B1321" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Chef de Projet Numérique Mode Agile Product Owner H/F</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Service Public</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1321" t="inlineStr">
+        <is>
+          <t>Large-scale public digital service delivery matches program-leadership breadth | Gap: Public-sector, non-financial, non-AI role well below Nicolas's seniority and domain focus</t>
+        </is>
+      </c>
+      <c r="M1321" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="B1322" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Product Owner Senior - Application Mobile H/F</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Celad</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1322" t="inlineStr">
+        <is>
+          <t>Senior title and international mobile app scope match some program-scale experience | Gap: Electrical-solutions sector via ESN staffing, no finance or AI relevance</t>
+        </is>
+      </c>
+      <c r="M1322" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="B1323" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Product Owner Senior Logiciel Métier International H/F</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>5 Degrés</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1323" t="inlineStr">
+        <is>
+          <t>International, multi-entity software platform ownership matches EMEA/Americas program experience | Gap: Generic ESN client engagement, unspecified sector, no AI relevance</t>
+        </is>
+      </c>
+      <c r="M1323" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="B1324" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Proxy Product Owner - Espace Client Pro Poste Ouvert aux CDI et Freelances H/F</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Inspiire</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1324" t="inlineStr">
+        <is>
+          <t>Freelance-eligible mission fits current freelance operating mode | Gap: Proxy PO doing test/QA support work is a junior operational role, well below 15+yr seniority</t>
+        </is>
+      </c>
+      <c r="M1324" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="B1325" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Chef de Produits Senior - Prêt à Porter Féminin H/F</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>SAYCO</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1325" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/sayco-152164.html</t>
+        </is>
+      </c>
+      <c r="L1325" t="inlineStr">
+        <is>
+          <t>Senior title indicates comparable seniority band | Gap: Fashion/apparel merchandising product role, entirely unrelated to finance, data or AI</t>
+        </is>
+      </c>
+      <c r="M1325" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="B1326" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Product Designer Cpo H/F</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Electra</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1326" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/electra-182816.html</t>
+        </is>
+      </c>
+      <c r="L1326" t="inlineStr">
+        <is>
+          <t>Fast-growing infrastructure scaleup offers CPO-adjacent product leadership exposure | Gap: EV-charging/hardware sector unrelated to finance/AI, role centers on design not PM ownership</t>
+        </is>
+      </c>
+      <c r="M1326" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="B1327" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Product Manager Discovery IA H/F</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Wold</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1327" t="inlineStr">
+        <is>
+          <t>Freelance AI product/consultant profile matches Nicolas's current freelance AI PoC and transformation background. | Gap: Role spans Supply Chain/Retail/Merchandising, not finance-specific; company 'Wold' unverified, not a target financial institution.</t>
+        </is>
+      </c>
+      <c r="M1327" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="B1328" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>R&amp;D Product Lifecycle &amp; Quality Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Pernod Ricard</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1328" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/pernod-ricard-153314.html</t>
+        </is>
+      </c>
+      <c r="L1328" t="inlineStr">
+        <is>
+          <t>15+ yrs cross-functional roadmap/stakeholder leadership transfers generically. | Gap: No financial services or AI relevance at all; wine &amp; spirits R&amp;D/quality domain is a hard mismatch.</t>
+        </is>
+      </c>
+      <c r="M1328" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="B1329" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Consultant Confirmé - Senior en Data Product Management H/F</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>People Fine</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L1329" t="inlineStr">
+        <is>
+          <t>Strong overlap with Data &amp; AI product ownership (Opensee ETL/pipeline, Dataiku, AI PoC experience). | Gap: Staffing/consulting firm role pitched as 'confirmé' (mid-senior IC), below Nicolas's Director/Head-level seniority.</t>
+        </is>
+      </c>
+      <c r="M1329" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="B1330" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Director of Product - RPG</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Homa Games</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1330" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010237720787</t>
+        </is>
+      </c>
+      <c r="L1330" t="inlineStr">
+        <is>
+          <t>Director-level title matches seniority; product/tech platform ownership experience transfers. | Gap: Mobile gaming domain has zero overlap with financial services, and AI is a platform feature not the product mandate.</t>
+        </is>
+      </c>
+      <c r="M1330" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="B1331" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Stagiaire / Alternant(e) Marketing &amp; Product Marketing</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Valeo SA</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1331" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010236022514</t>
+        </is>
+      </c>
+      <c r="L1331" t="inlineStr">
+        <is>
+          <t>None — automotive Marketing internship is entirely off-profile. | Gap: Intern/apprentice level role is a total seniority mismatch against 15+ yrs senior PM experience.</t>
+        </is>
+      </c>
+      <c r="M1331" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="B1332" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Senior Director, Product Management – Identity &amp; Trust</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>DocuSign, Inc.</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1332" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010234955682</t>
+        </is>
+      </c>
+      <c r="L1332" t="inlineStr">
+        <is>
+          <t>Senior Director seniority fits; Identity &amp; Trust and 'intelligent agreement management' echo AI-augmented enterprise SaaS product work. | Gap: DocuSign is a document/e-signature SaaS platform, not a financial services or named AI-first company on the target list.</t>
+        </is>
+      </c>
+      <c r="M1332" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="B1333" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Director, Product Partnerships H/F</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>American Express Company</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1333" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010232529765</t>
+        </is>
+      </c>
+      <c r="L1333" t="inlineStr">
+        <is>
+          <t>American Express is a top-tier financial/payments institution matching 15+ yrs financial-sector focus, and Director level fits seniority. | Gap: Role is Partnerships-led, not an AI/data product mandate — ai_relevance is essentially absent from the description.</t>
+        </is>
+      </c>
+      <c r="M1333" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="B1334" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Manager, Product Partnerships H/F</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>American Express Company</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1334" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010232529670</t>
+        </is>
+      </c>
+      <c r="L1334" t="inlineStr">
+        <is>
+          <t>Same strong financial-sector fit (Amex payments network) as the Director posting. | Gap: Manager-level title undershoots Nicolas's Director/Head-level seniority target, and no AI/data product angle.</t>
+        </is>
+      </c>
+      <c r="M1334" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="B1335" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Global Product Director Rare Oncology</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Les Laboratoires Servier</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1335" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010230992418</t>
+        </is>
+      </c>
+      <c r="L1335" t="inlineStr">
+        <is>
+          <t>Global Product Director title matches seniority level well. | Gap: Pharma/oncology domain has no financial services or AI-product relevance.</t>
+        </is>
+      </c>
+      <c r="M1335" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="B1336" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>DDAI PRODUCT DIRECTOR</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Danone S.A.</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1336" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010229004270</t>
+        </is>
+      </c>
+      <c r="L1336" t="inlineStr">
+        <is>
+          <t>DDAI (Data, Digital &amp; AI) Product Director role matches both AI-product mandate and Director-level seniority. | Gap: Danone is consumer packaged goods, not financial services or a named target company.</t>
+        </is>
+      </c>
+      <c r="M1336" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="B1337" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Product Manager Environnement de travail F/H (DSI/DWS)</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Régie Autonome des Transports Parisien</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1337" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010213462535</t>
+        </is>
+      </c>
+      <c r="L1337" t="inlineStr">
+        <is>
+          <t>Large-scale IT/Digital Workplace ownership (40k+ terminals) echoes program-scale delivery experience. | Gap: Workplace IT product role has no financial-sector or AI angle, and title reads as an operational PM, not a leadership mandate.</t>
+        </is>
+      </c>
+      <c r="M1337" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="B1338" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Director, Product Management – Fleet and Autonomous Vehicles US or Europe</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>ChargePoint, Inc.</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1338" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010214029933</t>
+        </is>
+      </c>
+      <c r="L1338" t="inlineStr">
+        <is>
+          <t>Director-level title matches seniority; large infra/platform product ownership transfers structurally. | Gap: EV charging/fleet domain has no financial services overlap and AI relevance is only tangential (autonomous vehicles, not AI product).</t>
+        </is>
+      </c>
+      <c r="M1338" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="B1339" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Senior Product Manager</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Curium</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1339" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010206862162</t>
+        </is>
+      </c>
+      <c r="L1339" t="inlineStr">
+        <is>
+          <t>Senior Product Manager title is broadly consistent with product ownership background. | Gap: Nuclear medicine/radiopharma is a hard domain mismatch with no finance or AI relevance.</t>
+        </is>
+      </c>
+      <c r="M1339" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="B1340" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Global Product Development Manager</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>The Estée Lauder Companies Inc.</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1340" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/j?jl=1010197852357</t>
+        </is>
+      </c>
+      <c r="L1340" t="inlineStr">
+        <is>
+          <t>Global scope product development experience is transferable at a structural level. | Gap: Luxury fragrance (Kilian Paris) has no financial services or AI-product relevance, and title suggests mid-level ownership, not Director/VP.</t>
+        </is>
+      </c>
+      <c r="M1340" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="B1341" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Senior Product Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="B1342" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Responsable Produit Série (F/H)</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="B1343" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Business Analyst / Product Owner - Lyon</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="B1344" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Consultant.e Product Designer</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="B1345" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Product Ops (H/F)</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="B1346" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Senior Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Brevo</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1346" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/brevo-165304.html</t>
+        </is>
+      </c>
+      <c r="L1346" t="inlineStr">
+        <is>
+          <t>Senior PM title and SaaS B2B platform experience transfer reasonably well. | Gap: Brevo (marketing/CRM SaaS) is outside financial services and not AI-centric; Senior (not Head/Director) undershoots seniority target.</t>
+        </is>
+      </c>
+      <c r="M1346" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="B1347" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Product Owner Digital H/F</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>KP2I</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="K1347" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/kp2i-116531.html</t>
+        </is>
+      </c>
+      <c r="L1347" t="inlineStr">
+        <is>
+          <t>IT/digital transformation consulting background is generically relevant. | Gap: Generic ESN-style Product Owner role with no finance or AI focus and no clear leadership seniority.</t>
+        </is>
+      </c>
+      <c r="M1347" t="inlineStr">
         <is>
           <t>Not yet applied</t>
         </is>

--- a/applications/Job_Matches_Paris_ProductAI.xlsx
+++ b/applications/Job_Matches_Paris_ProductAI.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1347"/>
+  <dimension ref="A1:M1370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -61609,6 +61609,869 @@
         </is>
       </c>
     </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr"/>
+      <c r="B1348" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - Agentic &amp; ai Automation H/F</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Believe</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr"/>
+      <c r="G1348" t="inlineStr"/>
+      <c r="H1348" t="inlineStr"/>
+      <c r="I1348" t="inlineStr"/>
+      <c r="J1348" t="inlineStr"/>
+      <c r="K1348" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/believe-91896.html</t>
+        </is>
+      </c>
+      <c r="L1348" t="inlineStr">
+        <is>
+          <t>Strength: AI relevance. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1348" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr"/>
+      <c r="B1349" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Product Manager B2b H/F</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Bloomays</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr"/>
+      <c r="G1349" t="inlineStr"/>
+      <c r="H1349" t="inlineStr"/>
+      <c r="I1349" t="inlineStr"/>
+      <c r="J1349" t="inlineStr"/>
+      <c r="L1349" t="inlineStr">
+        <is>
+          <t>Strength: finance/domain overlap. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1349" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr"/>
+      <c r="B1350" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Product Manager - Sales ai H/F</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr"/>
+      <c r="G1350" t="inlineStr"/>
+      <c r="H1350" t="inlineStr"/>
+      <c r="I1350" t="inlineStr"/>
+      <c r="J1350" t="inlineStr"/>
+      <c r="K1350" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/alan-116878.html</t>
+        </is>
+      </c>
+      <c r="L1350" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no named recruiter.</t>
+        </is>
+      </c>
+      <c r="M1350" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr"/>
+      <c r="B1351" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Technical Product Manager - Product Owner H/F</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Dev &amp; Connect</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr"/>
+      <c r="G1351" t="inlineStr"/>
+      <c r="H1351" t="inlineStr"/>
+      <c r="I1351" t="inlineStr"/>
+      <c r="J1351" t="inlineStr"/>
+      <c r="L1351" t="inlineStr">
+        <is>
+          <t>Strength: AI relevance. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1351" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr"/>
+      <c r="B1352" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Product Manager IA H/F</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>5 Degrés</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr"/>
+      <c r="G1352" t="inlineStr"/>
+      <c r="H1352" t="inlineStr"/>
+      <c r="I1352" t="inlineStr"/>
+      <c r="J1352" t="inlineStr"/>
+      <c r="L1352" t="inlineStr">
+        <is>
+          <t>Strength: AI relevance. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1352" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr"/>
+      <c r="B1353" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Product Manager Data H/F</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Yunik</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr"/>
+      <c r="G1353" t="inlineStr"/>
+      <c r="H1353" t="inlineStr"/>
+      <c r="I1353" t="inlineStr"/>
+      <c r="J1353" t="inlineStr"/>
+      <c r="L1353" t="inlineStr">
+        <is>
+          <t>Strength: finance/domain overlap. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1353" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr"/>
+      <c r="B1354" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Product Manager Officer H/F</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Caisse des Dépôts et Consignations (CDC)</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>Paris 13e - 75</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr"/>
+      <c r="G1354" t="inlineStr"/>
+      <c r="H1354" t="inlineStr"/>
+      <c r="I1354" t="inlineStr"/>
+      <c r="J1354" t="inlineStr"/>
+      <c r="L1354" t="inlineStr">
+        <is>
+          <t>Strength: finance/domain overlap. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1354" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr"/>
+      <c r="B1355" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - User And Lifecycle Analytics H/F</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Contentsquare</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr"/>
+      <c r="G1355" t="inlineStr"/>
+      <c r="H1355" t="inlineStr"/>
+      <c r="I1355" t="inlineStr"/>
+      <c r="J1355" t="inlineStr"/>
+      <c r="K1355" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/contentsquare-97142.html</t>
+        </is>
+      </c>
+      <c r="L1355" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: limited AI-specific scope.</t>
+        </is>
+      </c>
+      <c r="M1355" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr"/>
+      <c r="B1356" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Responsable du pôle Product Management - Secteur Energie F/H</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>Groupe Talents Handicap</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>Nanterre</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr"/>
+      <c r="G1356" t="inlineStr"/>
+      <c r="H1356" t="inlineStr"/>
+      <c r="I1356" t="inlineStr"/>
+      <c r="J1356" t="inlineStr"/>
+      <c r="K1356" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.fr/job-listing/responsable-du-pôle-product-management-secteur-energie-fh-groupe-talents-handicap-JV_IC3019245_KO0,57_KE58,81.htm?jl=1010245287964</t>
+        </is>
+      </c>
+      <c r="L1356" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1356" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr"/>
+      <c r="B1357" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Product Manager Data &amp; ai Platform H/F</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Wold</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr"/>
+      <c r="G1357" t="inlineStr"/>
+      <c r="H1357" t="inlineStr"/>
+      <c r="I1357" t="inlineStr"/>
+      <c r="J1357" t="inlineStr"/>
+      <c r="L1357" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1357" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr"/>
+      <c r="B1358" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - ai H/F</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr"/>
+      <c r="G1358" t="inlineStr"/>
+      <c r="H1358" t="inlineStr"/>
+      <c r="I1358" t="inlineStr"/>
+      <c r="J1358" t="inlineStr"/>
+      <c r="K1358" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/front-107796.html</t>
+        </is>
+      </c>
+      <c r="L1358" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1358" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr"/>
+      <c r="B1359" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Dicom 75 - Responsable de l'Unité Produit - Head Of Product Sic H/F</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Service Public</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr"/>
+      <c r="G1359" t="inlineStr"/>
+      <c r="H1359" t="inlineStr"/>
+      <c r="I1359" t="inlineStr"/>
+      <c r="J1359" t="inlineStr"/>
+      <c r="L1359" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1359" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr"/>
+      <c r="B1360" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Senior Data Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>LittleBig Connection (part of Mantu)</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr"/>
+      <c r="G1360" t="inlineStr"/>
+      <c r="H1360" t="inlineStr"/>
+      <c r="I1360" t="inlineStr"/>
+      <c r="J1360" t="inlineStr"/>
+      <c r="L1360" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1360" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr"/>
+      <c r="B1361" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Product Manager Discovery IA H/F</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>Wold</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr"/>
+      <c r="G1361" t="inlineStr"/>
+      <c r="H1361" t="inlineStr"/>
+      <c r="I1361" t="inlineStr"/>
+      <c r="J1361" t="inlineStr"/>
+      <c r="L1361" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1361" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr"/>
+      <c r="B1362" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Senior Technical Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>Murex</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr"/>
+      <c r="G1362" t="inlineStr"/>
+      <c r="H1362" t="inlineStr"/>
+      <c r="I1362" t="inlineStr"/>
+      <c r="J1362" t="inlineStr"/>
+      <c r="K1362" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/murex-108701.html</t>
+        </is>
+      </c>
+      <c r="L1362" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1362" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr"/>
+      <c r="B1363" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Product Manager Senior Mobile - CDI H/F</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>SprintMob</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr"/>
+      <c r="G1363" t="inlineStr"/>
+      <c r="H1363" t="inlineStr"/>
+      <c r="I1363" t="inlineStr"/>
+      <c r="J1363" t="inlineStr"/>
+      <c r="L1363" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1363" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr"/>
+      <c r="B1364" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Product Manager Poste de Travail Sécurisé H/F</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>Service Public</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>Paris 7e - 75</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr"/>
+      <c r="G1364" t="inlineStr"/>
+      <c r="H1364" t="inlineStr"/>
+      <c r="I1364" t="inlineStr"/>
+      <c r="J1364" t="inlineStr"/>
+      <c r="L1364" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1364" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr"/>
+      <c r="B1365" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Chef - Cheffe de Produit ai Factory France H/F</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>INRIA - Institut national de recherche en sciences et technologies du numérique</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr"/>
+      <c r="G1365" t="inlineStr"/>
+      <c r="H1365" t="inlineStr"/>
+      <c r="I1365" t="inlineStr"/>
+      <c r="J1365" t="inlineStr"/>
+      <c r="L1365" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1365" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr"/>
+      <c r="B1366" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Product Manager Média H/F</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>5 Degrés</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr"/>
+      <c r="G1366" t="inlineStr"/>
+      <c r="H1366" t="inlineStr"/>
+      <c r="I1366" t="inlineStr"/>
+      <c r="J1366" t="inlineStr"/>
+      <c r="L1366" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1366" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr"/>
+      <c r="B1367" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Sgps - Product Manager H/F</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>Agence Nationale de l'Habitat (ANAH)</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr"/>
+      <c r="G1367" t="inlineStr"/>
+      <c r="H1367" t="inlineStr"/>
+      <c r="I1367" t="inlineStr"/>
+      <c r="J1367" t="inlineStr"/>
+      <c r="L1367" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1367" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr"/>
+      <c r="B1368" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Chef de Produit Applicatif IA H/F</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>Service Public</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>Paris 7e - 75</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr"/>
+      <c r="G1368" t="inlineStr"/>
+      <c r="H1368" t="inlineStr"/>
+      <c r="I1368" t="inlineStr"/>
+      <c r="J1368" t="inlineStr"/>
+      <c r="L1368" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1368" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr"/>
+      <c r="B1369" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Product Engineer Python - React - Nextjs H/F</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Zenior</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr"/>
+      <c r="G1369" t="inlineStr"/>
+      <c r="H1369" t="inlineStr"/>
+      <c r="I1369" t="inlineStr"/>
+      <c r="J1369" t="inlineStr"/>
+      <c r="L1369" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1369" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr"/>
+      <c r="B1370" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>CDI - Chef de Produit Prêt-À-Porter H/F</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>Chanel</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>Paris - 75</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr"/>
+      <c r="G1370" t="inlineStr"/>
+      <c r="H1370" t="inlineStr"/>
+      <c r="I1370" t="inlineStr"/>
+      <c r="J1370" t="inlineStr"/>
+      <c r="K1370" t="inlineStr">
+        <is>
+          <t>https://www.hellowork.com/fr-fr/entreprises/chanel-88659.html</t>
+        </is>
+      </c>
+      <c r="L1370" t="inlineStr">
+        <is>
+          <t>Strength: seniority fit. Gap: no target-sector bonus.</t>
+        </is>
+      </c>
+      <c r="M1370" t="inlineStr">
+        <is>
+          <t>Not yet applied</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
